--- a/media/uploads/product/product_sample_file_1.xlsx
+++ b/media/uploads/product/product_sample_file_1.xlsx
@@ -74,22 +74,22 @@
     <t xml:space="preserve">notes</t>
   </si>
   <si>
-    <t xml:space="preserve">status</t>
+    <t xml:space="preserve">product_status</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Samsung12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Electronics</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Others</t>
   </si>
   <si>
     <t xml:space="preserve">Samsung</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Electronics</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Component Parts</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Consumer Products</t>
   </si>
   <si>
     <t xml:space="preserve">Hyundai</t>
@@ -236,32 +236,36 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -516,10 +520,6 @@
   </sheetPr>
   <dimension ref="A1:R2"/>
   <sheetFormatPr defaultColWidth="8.6015625" defaultRowHeight="13.5" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
-  <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="0" width="10.63"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="18" style="0" width="18.29"/>
-  </cols>
   <sheetData>
     <row r="1" s="1" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
@@ -578,68 +578,62 @@
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="s">
+      <c r="A2" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="B2" s="0" t="s">
+      <c r="B2" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="C2" s="0" t="s">
+      <c r="C2" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="D2" s="0" t="s">
+      <c r="D2" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="E2" s="0" t="s">
+      <c r="E2" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="F2" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="F2" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="G2" s="3" t="s">
+      <c r="G2" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="H2" s="4" t="s">
+      <c r="H2" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="I2" s="5" t="s">
+      <c r="I2" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="J2" s="4" t="s">
+      <c r="J2" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="K2" s="4" t="s">
+      <c r="K2" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="L2" s="4" t="s">
+      <c r="L2" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="M2" s="4" t="n">
+      <c r="M2" s="5" t="n">
         <v>1234</v>
       </c>
-      <c r="N2" s="4" t="n">
+      <c r="N2" s="5" t="n">
         <v>5678</v>
       </c>
-      <c r="O2" s="4" t="s">
+      <c r="O2" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="P2" s="6" t="n">
+      <c r="P2" s="7" t="n">
         <v>123500000000</v>
       </c>
-      <c r="Q2" s="4" t="s">
+      <c r="Q2" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="R2" s="4" t="s">
+      <c r="R2" s="5" t="s">
         <v>31</v>
       </c>
     </row>
   </sheetData>
-  <dataValidations count="1">
-    <dataValidation allowBlank="true" errorStyle="stop" operator="equal" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="R2" type="list">
-      <formula1>"Active,InActive,Draft,,"</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
-  </dataValidations>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
